--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9A7CBB-CEC6-4F9C-99C8-7AD1347F2E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750479C3-F75D-4284-A068-4FCDD5C4517F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5D88B24-62E4-4111-9F6C-95262D24FDD6}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964" xr2:uid="{F5D88B24-62E4-4111-9F6C-95262D24FDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,47 +34,91 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Itemcategory</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Base UOM</t>
-  </si>
-  <si>
-    <t>Transaction UOM</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Multiplier</t>
   </si>
   <si>
-    <t>TaxProfile</t>
-  </si>
-  <si>
-    <t>IMS-NNT Private Limited</t>
+    <t>ItemCategory</t>
+  </si>
+  <si>
+    <t>ItemSubcategory</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>ItemsName</t>
+  </si>
+  <si>
+    <t>TaxRate</t>
+  </si>
+  <si>
+    <t>PriceType</t>
+  </si>
+  <si>
+    <t>BaseUOM</t>
+  </si>
+  <si>
+    <t>TransactionUOM</t>
+  </si>
+  <si>
+    <t>SellingItemAs(Good/Services)</t>
+  </si>
+  <si>
+    <t>IsCessApplied</t>
+  </si>
+  <si>
+    <t>Cess(%)</t>
+  </si>
+  <si>
+    <t>HSNCode</t>
+  </si>
+  <si>
+    <t>SafetyQty</t>
+  </si>
+  <si>
+    <t>PurchasePrice</t>
+  </si>
+  <si>
+    <t>StandardSalePrice</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Ingredients</t>
+  </si>
+  <si>
+    <t>Description[BarCode]</t>
+  </si>
+  <si>
+    <t>IsManufacturingItem</t>
+  </si>
+  <si>
+    <t>IsPackingItem</t>
+  </si>
+  <si>
+    <t>QuantityMultiplier</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Item Barcode</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -86,6 +130,16 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -102,7 +156,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -114,7 +168,9 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -124,68 +180,46 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{5F993620-F1A8-4A7A-8347-FB20501CECCB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -497,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6320A580-F700-457D-99AA-D7681DDA5FD5}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -509,42 +543,94 @@
     <col min="7" max="7" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:25" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>